--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Debt Management Fund (FOF).xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Debt Management Fund (FOF).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Debt Management Fund (FOF)</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -88,16 +88,10 @@
     <t>INF109KA1O37</t>
   </si>
   <si>
-    <t>HDFC Nifty G-Sec June 2027 Index Fund - Direct Plan - Growth</t>
-  </si>
-  <si>
-    <t>INF179KC1EJ8</t>
-  </si>
-  <si>
-    <t>HDFC Ultra Short Term Fund - Direct - Growth</t>
-  </si>
-  <si>
-    <t>INF179KB15Q6</t>
+    <t>Bandhan Govt Securities Fund Investment Plan - Direct - Growth</t>
+  </si>
+  <si>
+    <t>INF194K01Q29</t>
   </si>
   <si>
     <t>TREPS</t>
@@ -115,7 +109,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -127,7 +121,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - CRISIL Composite Bond Index</t>
+    <t>Benchmark name - CRISIL Composite Bond Fund Index</t>
   </si>
 </sst>
 </file>
@@ -430,13 +424,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -454,7 +448,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="5791200"/>
+          <a:off x="666750" y="5600700"/>
           <a:ext cx="4562475" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -469,13 +463,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>52</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -493,7 +487,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="8648700"/>
+          <a:off x="666750" y="8458200"/>
           <a:ext cx="4562475" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -827,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J42"/>
+  <dimension ref="B1:J41"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
@@ -921,10 +915,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="9">
-        <v>11008.33</v>
+        <v>11216.49</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9703666381658</v>
+        <v>0.9721766222379</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>12</v>
@@ -947,10 +941,10 @@
         <v>11489378.465</v>
       </c>
       <c r="F6" s="15">
-        <v>4400.31</v>
+        <v>4595.76</v>
       </c>
       <c r="G6" s="16">
-        <v>0.387880270812</v>
+        <v>0.3983323154941</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>12</v>
@@ -973,10 +967,10 @@
         <v>5832596.203</v>
       </c>
       <c r="F7" s="15">
-        <v>3673.04</v>
+        <v>3822.92</v>
       </c>
       <c r="G7" s="16">
-        <v>0.3237725864549</v>
+        <v>0.3313472800035</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>12</v>
@@ -999,10 +993,10 @@
         <v>3054780.689</v>
       </c>
       <c r="F8" s="15">
-        <v>1441.90</v>
+        <v>1501.36</v>
       </c>
       <c r="G8" s="16">
-        <v>0.1271011729818</v>
+        <v>0.1301286849596</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>12</v>
@@ -1022,13 +1016,13 @@
         <v>15</v>
       </c>
       <c r="E9" s="14">
-        <v>139373.333</v>
+        <v>103865.379</v>
       </c>
       <c r="F9" s="15">
-        <v>621.37</v>
+        <v>479.47</v>
       </c>
       <c r="G9" s="16">
-        <v>0.0547727691627</v>
+        <v>0.0415575215655</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>12</v>
@@ -1048,13 +1042,13 @@
         <v>15</v>
       </c>
       <c r="E10" s="14">
-        <v>2428656.051</v>
+        <v>1603158.07</v>
       </c>
       <c r="F10" s="15">
-        <v>586.94</v>
+        <v>409.10</v>
       </c>
       <c r="G10" s="16">
-        <v>0.0517378198696</v>
+        <v>0.0354582811697</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>12</v>
@@ -1074,13 +1068,13 @@
         <v>15</v>
       </c>
       <c r="E11" s="14">
-        <v>1759375.426</v>
+        <v>1053955.778</v>
       </c>
       <c r="F11" s="15">
-        <v>206.22</v>
+        <v>407.88</v>
       </c>
       <c r="G11" s="16">
-        <v>0.018177962336</v>
+        <v>0.0353525390455</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>12</v>
@@ -1091,157 +1085,131 @@
     </row>
     <row r="12" spans="2:9" ht="15" customHeight="1">
       <c r="B12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="15" customHeight="1">
+      <c r="B13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="9">
+        <v>350.23</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.0303557903057</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="15" customHeight="1">
+      <c r="B14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="15" customHeight="1">
+      <c r="B15" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="14">
-        <v>524399.693</v>
-      </c>
-      <c r="F12" s="15">
-        <v>78.55</v>
-      </c>
-      <c r="G12" s="16">
-        <v>0.0069240565488</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="15" customHeight="1">
-      <c r="B13" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="15" customHeight="1">
-      <c r="B14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="9">
-        <v>344.29</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0.0303486114473</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" ht="15" customHeight="1">
-      <c r="B15" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="11" t="s">
+      <c r="C15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="18">
+        <v>-29.217715509999834</v>
+      </c>
+      <c r="G15" s="19">
+        <v>-0.0025324125438551423</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" customHeight="1">
       <c r="B16" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="18">
+        <v>11537.50228449</v>
+      </c>
+      <c r="G16" s="19">
+        <v>0.9999999999997448</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="18">
-        <v>-8.114153420001458</v>
-      </c>
-      <c r="G16" s="19">
-        <v>-0.0007152496133137092</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="15" customHeight="1">
-      <c r="B17" s="17" t="s">
+    </row>
+    <row r="20" ht="27.5" customHeight="1">
+      <c r="B20" s="20" t="s">
         <v>30</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="18">
-        <v>11344.50584658</v>
-      </c>
-      <c r="G17" s="19">
-        <v>0.9999999999997864</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="13" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="21" ht="27.5" customHeight="1">
       <c r="B21" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" ht="27.5" customHeight="1">
       <c r="B22" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="15">
+      <c r="B25" s="21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" ht="27.5" customHeight="1">
-      <c r="B23" s="20" t="s">
+    <row r="40" ht="15">
+      <c r="B40" s="21" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="26" ht="15">
-      <c r="B26" s="21" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="41" ht="15">
       <c r="B41" s="21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" ht="15">
-      <c r="B42" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1249,10 +1217,10 @@
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B19:H19"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B23:H23"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
